--- a/outputs/52575.xlsx
+++ b/outputs/52575.xlsx
@@ -133,21 +133,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -407,8 +411,8 @@
       <c r="E2" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F2" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E2,$B$2:$B$92,$B2,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E2,$B$2:$B$92,$B2,$D$2:$D$92,"Overtime")&gt;0,$E2&lt;&gt;$E1),"y","")</f>
+      <c r="F2" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B2,$E$2:$E92,$E2,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B2,$E$2:$E92,$E2,$D$2:$D92,"Overtime")&gt;0,$E2&lt;&gt;$E1),"y","")</f>
         <v>y</v>
       </c>
     </row>
@@ -425,8 +429,8 @@
       <c r="E3" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F3" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E3,$B$2:$B$92,$B3,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E3,$B$2:$B$92,$B3,$D$2:$D$92,"Overtime")&gt;0,$E3&lt;&gt;$E2),"y","")</f>
+      <c r="F3" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B3,$E$2:$E92,$E3,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B3,$E$2:$E92,$E3,$D$2:$D92,"Overtime")&gt;0,$E3&lt;&gt;$E2),"y","")</f>
         <v/>
       </c>
     </row>
@@ -443,8 +447,8 @@
       <c r="E4" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F4" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E4,$B$2:$B$92,$B4,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E4,$B$2:$B$92,$B4,$D$2:$D$92,"Overtime")&gt;0,$E4&lt;&gt;$E3),"y","")</f>
+      <c r="F4" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B4,$E$2:$E92,$E4,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B4,$E$2:$E92,$E4,$D$2:$D92,"Overtime")&gt;0,$E4&lt;&gt;$E3),"y","")</f>
         <v/>
       </c>
     </row>
@@ -458,8 +462,8 @@
       <c r="E5" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F5" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E5,$B$2:$B$92,$B5,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E5,$B$2:$B$92,$B5,$D$2:$D$92,"Overtime")&gt;0,$E5&lt;&gt;$E4),"y","")</f>
+      <c r="F5" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B5,$E$2:$E92,$E5,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B5,$E$2:$E92,$E5,$D$2:$D92,"Overtime")&gt;0,$E5&lt;&gt;$E4),"y","")</f>
         <v/>
       </c>
     </row>
@@ -473,8 +477,8 @@
       <c r="E6" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E6,$B$2:$B$92,$B6,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E6,$B$2:$B$92,$B6,$D$2:$D$92,"Overtime")&gt;0,$E6&lt;&gt;$E5),"y","")</f>
+      <c r="F6" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B6,$E$2:$E92,$E6,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B6,$E$2:$E92,$E6,$D$2:$D92,"Overtime")&gt;0,$E6&lt;&gt;$E5),"y","")</f>
         <v/>
       </c>
     </row>
@@ -488,8 +492,8 @@
       <c r="E7" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F7" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E7,$B$2:$B$92,$B7,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E7,$B$2:$B$92,$B7,$D$2:$D$92,"Overtime")&gt;0,$E7&lt;&gt;$E6),"y","")</f>
+      <c r="F7" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B7,$E$2:$E92,$E7,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B7,$E$2:$E92,$E7,$D$2:$D92,"Overtime")&gt;0,$E7&lt;&gt;$E6),"y","")</f>
         <v/>
       </c>
     </row>
@@ -503,8 +507,8 @@
       <c r="E8" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F8" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E8,$B$2:$B$92,$B8,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E8,$B$2:$B$92,$B8,$D$2:$D$92,"Overtime")&gt;0,$E8&lt;&gt;$E7),"y","")</f>
+      <c r="F8" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B8,$E$2:$E92,$E8,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B8,$E$2:$E92,$E8,$D$2:$D92,"Overtime")&gt;0,$E8&lt;&gt;$E7),"y","")</f>
         <v/>
       </c>
     </row>
@@ -518,8 +522,8 @@
       <c r="E9" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F9" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E9,$B$2:$B$92,$B9,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E9,$B$2:$B$92,$B9,$D$2:$D$92,"Overtime")&gt;0,$E9&lt;&gt;$E8),"y","")</f>
+      <c r="F9" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B9,$E$2:$E92,$E9,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B9,$E$2:$E92,$E9,$D$2:$D92,"Overtime")&gt;0,$E9&lt;&gt;$E8),"y","")</f>
         <v/>
       </c>
     </row>
@@ -533,8 +537,8 @@
       <c r="E10" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F10" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E10,$B$2:$B$92,$B10,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E10,$B$2:$B$92,$B10,$D$2:$D$92,"Overtime")&gt;0,$E10&lt;&gt;$E9),"y","")</f>
+      <c r="F10" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B10,$E$2:$E92,$E10,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B10,$E$2:$E92,$E10,$D$2:$D92,"Overtime")&gt;0,$E10&lt;&gt;$E9),"y","")</f>
         <v/>
       </c>
     </row>
@@ -548,8 +552,8 @@
       <c r="E11" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F11" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E11,$B$2:$B$92,$B11,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E11,$B$2:$B$92,$B11,$D$2:$D$92,"Overtime")&gt;0,$E11&lt;&gt;$E10),"y","")</f>
+      <c r="F11" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B11,$E$2:$E92,$E11,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B11,$E$2:$E92,$E11,$D$2:$D92,"Overtime")&gt;0,$E11&lt;&gt;$E10),"y","")</f>
         <v/>
       </c>
     </row>
@@ -563,8 +567,8 @@
       <c r="E12" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F12" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E12,$B$2:$B$92,$B12,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E12,$B$2:$B$92,$B12,$D$2:$D$92,"Overtime")&gt;0,$E12&lt;&gt;$E11),"y","")</f>
+      <c r="F12" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B12,$E$2:$E92,$E12,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B12,$E$2:$E92,$E12,$D$2:$D92,"Overtime")&gt;0,$E12&lt;&gt;$E11),"y","")</f>
         <v/>
       </c>
     </row>
@@ -578,8 +582,8 @@
       <c r="E13" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F13" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E13,$B$2:$B$92,$B13,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E13,$B$2:$B$92,$B13,$D$2:$D$92,"Overtime")&gt;0,$E13&lt;&gt;$E12),"y","")</f>
+      <c r="F13" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B13,$E$2:$E92,$E13,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B13,$E$2:$E92,$E13,$D$2:$D92,"Overtime")&gt;0,$E13&lt;&gt;$E12),"y","")</f>
         <v/>
       </c>
     </row>
@@ -593,8 +597,8 @@
       <c r="E14" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F14" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E14,$B$2:$B$92,$B14,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E14,$B$2:$B$92,$B14,$D$2:$D$92,"Overtime")&gt;0,$E14&lt;&gt;$E13),"y","")</f>
+      <c r="F14" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B14,$E$2:$E92,$E14,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B14,$E$2:$E92,$E14,$D$2:$D92,"Overtime")&gt;0,$E14&lt;&gt;$E13),"y","")</f>
         <v>y</v>
       </c>
     </row>
@@ -611,8 +615,8 @@
       <c r="E15" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F15" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E15,$B$2:$B$92,$B15,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E15,$B$2:$B$92,$B15,$D$2:$D$92,"Overtime")&gt;0,$E15&lt;&gt;$E14),"y","")</f>
+      <c r="F15" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B15,$E$2:$E92,$E15,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B15,$E$2:$E92,$E15,$D$2:$D92,"Overtime")&gt;0,$E15&lt;&gt;$E14),"y","")</f>
         <v/>
       </c>
     </row>
@@ -626,8 +630,8 @@
       <c r="E16" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F16" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E16,$B$2:$B$92,$B16,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E16,$B$2:$B$92,$B16,$D$2:$D$92,"Overtime")&gt;0,$E16&lt;&gt;$E15),"y","")</f>
+      <c r="F16" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B16,$E$2:$E92,$E16,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B16,$E$2:$E92,$E16,$D$2:$D92,"Overtime")&gt;0,$E16&lt;&gt;$E15),"y","")</f>
         <v/>
       </c>
     </row>
@@ -641,8 +645,8 @@
       <c r="E17" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F17" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E17,$B$2:$B$92,$B17,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E17,$B$2:$B$92,$B17,$D$2:$D$92,"Overtime")&gt;0,$E17&lt;&gt;$E16),"y","")</f>
+      <c r="F17" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B17,$E$2:$E92,$E17,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B17,$E$2:$E92,$E17,$D$2:$D92,"Overtime")&gt;0,$E17&lt;&gt;$E16),"y","")</f>
         <v/>
       </c>
     </row>
@@ -659,8 +663,8 @@
       <c r="E18" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F18" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E18,$B$2:$B$92,$B18,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E18,$B$2:$B$92,$B18,$D$2:$D$92,"Overtime")&gt;0,$E18&lt;&gt;$E17),"y","")</f>
+      <c r="F18" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B18,$E$2:$E92,$E18,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B18,$E$2:$E92,$E18,$D$2:$D92,"Overtime")&gt;0,$E18&lt;&gt;$E17),"y","")</f>
         <v/>
       </c>
     </row>
@@ -674,8 +678,8 @@
       <c r="E19" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F19" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E19,$B$2:$B$92,$B19,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E19,$B$2:$B$92,$B19,$D$2:$D$92,"Overtime")&gt;0,$E19&lt;&gt;$E18),"y","")</f>
+      <c r="F19" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B19,$E$2:$E92,$E19,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B19,$E$2:$E92,$E19,$D$2:$D92,"Overtime")&gt;0,$E19&lt;&gt;$E18),"y","")</f>
         <v/>
       </c>
     </row>
@@ -689,8 +693,8 @@
       <c r="E20" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F20" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E20,$B$2:$B$92,$B20,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E20,$B$2:$B$92,$B20,$D$2:$D$92,"Overtime")&gt;0,$E20&lt;&gt;$E19),"y","")</f>
+      <c r="F20" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B20,$E$2:$E92,$E20,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B20,$E$2:$E92,$E20,$D$2:$D92,"Overtime")&gt;0,$E20&lt;&gt;$E19),"y","")</f>
         <v/>
       </c>
     </row>
@@ -704,8 +708,8 @@
       <c r="E21" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F21" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E21,$B$2:$B$92,$B21,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E21,$B$2:$B$92,$B21,$D$2:$D$92,"Overtime")&gt;0,$E21&lt;&gt;$E20),"y","")</f>
+      <c r="F21" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B21,$E$2:$E92,$E21,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B21,$E$2:$E92,$E21,$D$2:$D92,"Overtime")&gt;0,$E21&lt;&gt;$E20),"y","")</f>
         <v/>
       </c>
     </row>
@@ -719,8 +723,8 @@
       <c r="E22" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F22" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E22,$B$2:$B$92,$B22,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E22,$B$2:$B$92,$B22,$D$2:$D$92,"Overtime")&gt;0,$E22&lt;&gt;$E21),"y","")</f>
+      <c r="F22" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B22,$E$2:$E92,$E22,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B22,$E$2:$E92,$E22,$D$2:$D92,"Overtime")&gt;0,$E22&lt;&gt;$E21),"y","")</f>
         <v/>
       </c>
     </row>
@@ -734,8 +738,8 @@
       <c r="E23" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F23" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E23,$B$2:$B$92,$B23,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E23,$B$2:$B$92,$B23,$D$2:$D$92,"Overtime")&gt;0,$E23&lt;&gt;$E22),"y","")</f>
+      <c r="F23" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B23,$E$2:$E92,$E23,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B23,$E$2:$E92,$E23,$D$2:$D92,"Overtime")&gt;0,$E23&lt;&gt;$E22),"y","")</f>
         <v/>
       </c>
     </row>
@@ -749,8 +753,8 @@
       <c r="E24" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F24" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E24,$B$2:$B$92,$B24,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E24,$B$2:$B$92,$B24,$D$2:$D$92,"Overtime")&gt;0,$E24&lt;&gt;$E23),"y","")</f>
+      <c r="F24" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B24,$E$2:$E92,$E24,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B24,$E$2:$E92,$E24,$D$2:$D92,"Overtime")&gt;0,$E24&lt;&gt;$E23),"y","")</f>
         <v/>
       </c>
     </row>
@@ -764,8 +768,8 @@
       <c r="E25" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F25" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E25,$B$2:$B$92,$B25,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E25,$B$2:$B$92,$B25,$D$2:$D$92,"Overtime")&gt;0,$E25&lt;&gt;$E24),"y","")</f>
+      <c r="F25" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B25,$E$2:$E92,$E25,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B25,$E$2:$E92,$E25,$D$2:$D92,"Overtime")&gt;0,$E25&lt;&gt;$E24),"y","")</f>
         <v/>
       </c>
     </row>
@@ -779,8 +783,8 @@
       <c r="E26" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F26" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E26,$B$2:$B$92,$B26,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E26,$B$2:$B$92,$B26,$D$2:$D$92,"Overtime")&gt;0,$E26&lt;&gt;$E25),"y","")</f>
+      <c r="F26" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B26,$E$2:$E92,$E26,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B26,$E$2:$E92,$E26,$D$2:$D92,"Overtime")&gt;0,$E26&lt;&gt;$E25),"y","")</f>
         <v/>
       </c>
     </row>
@@ -794,8 +798,8 @@
       <c r="E27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F27" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E27,$B$2:$B$92,$B27,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E27,$B$2:$B$92,$B27,$D$2:$D$92,"Overtime")&gt;0,$E27&lt;&gt;$E26),"y","")</f>
+      <c r="F27" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B27,$E$2:$E92,$E27,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B27,$E$2:$E92,$E27,$D$2:$D92,"Overtime")&gt;0,$E27&lt;&gt;$E26),"y","")</f>
         <v/>
       </c>
     </row>
@@ -809,8 +813,8 @@
       <c r="E28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F28" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E28,$B$2:$B$92,$B28,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E28,$B$2:$B$92,$B28,$D$2:$D$92,"Overtime")&gt;0,$E28&lt;&gt;$E27),"y","")</f>
+      <c r="F28" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B28,$E$2:$E92,$E28,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B28,$E$2:$E92,$E28,$D$2:$D92,"Overtime")&gt;0,$E28&lt;&gt;$E27),"y","")</f>
         <v/>
       </c>
     </row>
@@ -824,8 +828,8 @@
       <c r="E29" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F29" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E29,$B$2:$B$92,$B29,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E29,$B$2:$B$92,$B29,$D$2:$D$92,"Overtime")&gt;0,$E29&lt;&gt;$E28),"y","")</f>
+      <c r="F29" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B29,$E$2:$E92,$E29,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B29,$E$2:$E92,$E29,$D$2:$D92,"Overtime")&gt;0,$E29&lt;&gt;$E28),"y","")</f>
         <v/>
       </c>
     </row>
@@ -839,8 +843,8 @@
       <c r="E30" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F30" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E30,$B$2:$B$92,$B30,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E30,$B$2:$B$92,$B30,$D$2:$D$92,"Overtime")&gt;0,$E30&lt;&gt;$E29),"y","")</f>
+      <c r="F30" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B30,$E$2:$E92,$E30,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B30,$E$2:$E92,$E30,$D$2:$D92,"Overtime")&gt;0,$E30&lt;&gt;$E29),"y","")</f>
         <v/>
       </c>
     </row>
@@ -854,8 +858,8 @@
       <c r="E31" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F31" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E31,$B$2:$B$92,$B31,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E31,$B$2:$B$92,$B31,$D$2:$D$92,"Overtime")&gt;0,$E31&lt;&gt;$E30),"y","")</f>
+      <c r="F31" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B31,$E$2:$E92,$E31,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B31,$E$2:$E92,$E31,$D$2:$D92,"Overtime")&gt;0,$E31&lt;&gt;$E30),"y","")</f>
         <v/>
       </c>
     </row>
@@ -869,8 +873,8 @@
       <c r="E32" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F32" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E32,$B$2:$B$92,$B32,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E32,$B$2:$B$92,$B32,$D$2:$D$92,"Overtime")&gt;0,$E32&lt;&gt;$E31),"y","")</f>
+      <c r="F32" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B32,$E$2:$E92,$E32,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B32,$E$2:$E92,$E32,$D$2:$D92,"Overtime")&gt;0,$E32&lt;&gt;$E31),"y","")</f>
         <v/>
       </c>
     </row>
@@ -884,8 +888,8 @@
       <c r="E33" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F33" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E33,$B$2:$B$92,$B33,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E33,$B$2:$B$92,$B33,$D$2:$D$92,"Overtime")&gt;0,$E33&lt;&gt;$E32),"y","")</f>
+      <c r="F33" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B33,$E$2:$E92,$E33,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B33,$E$2:$E92,$E33,$D$2:$D92,"Overtime")&gt;0,$E33&lt;&gt;$E32),"y","")</f>
         <v/>
       </c>
     </row>
@@ -899,8 +903,8 @@
       <c r="E34" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F34" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E34,$B$2:$B$92,$B34,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E34,$B$2:$B$92,$B34,$D$2:$D$92,"Overtime")&gt;0,$E34&lt;&gt;$E33),"y","")</f>
+      <c r="F34" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B34,$E$2:$E92,$E34,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B34,$E$2:$E92,$E34,$D$2:$D92,"Overtime")&gt;0,$E34&lt;&gt;$E33),"y","")</f>
         <v/>
       </c>
     </row>
@@ -914,8 +918,8 @@
       <c r="E35" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F35" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E35,$B$2:$B$92,$B35,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E35,$B$2:$B$92,$B35,$D$2:$D$92,"Overtime")&gt;0,$E35&lt;&gt;$E34),"y","")</f>
+      <c r="F35" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B35,$E$2:$E92,$E35,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B35,$E$2:$E92,$E35,$D$2:$D92,"Overtime")&gt;0,$E35&lt;&gt;$E34),"y","")</f>
         <v/>
       </c>
     </row>
@@ -929,8 +933,8 @@
       <c r="E36" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F36" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E36,$B$2:$B$92,$B36,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E36,$B$2:$B$92,$B36,$D$2:$D$92,"Overtime")&gt;0,$E36&lt;&gt;$E35),"y","")</f>
+      <c r="F36" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B36,$E$2:$E92,$E36,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B36,$E$2:$E92,$E36,$D$2:$D92,"Overtime")&gt;0,$E36&lt;&gt;$E35),"y","")</f>
         <v/>
       </c>
     </row>
@@ -944,8 +948,8 @@
       <c r="E37" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F37" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E37,$B$2:$B$92,$B37,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E37,$B$2:$B$92,$B37,$D$2:$D$92,"Overtime")&gt;0,$E37&lt;&gt;$E36),"y","")</f>
+      <c r="F37" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B37,$E$2:$E92,$E37,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B37,$E$2:$E92,$E37,$D$2:$D92,"Overtime")&gt;0,$E37&lt;&gt;$E36),"y","")</f>
         <v/>
       </c>
     </row>
@@ -959,8 +963,8 @@
       <c r="E38" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="F38" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E38,$B$2:$B$92,$B38,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E38,$B$2:$B$92,$B38,$D$2:$D$92,"Overtime")&gt;0,$E38&lt;&gt;$E37),"y","")</f>
+      <c r="F38" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B38,$E$2:$E92,$E38,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B38,$E$2:$E92,$E38,$D$2:$D92,"Overtime")&gt;0,$E38&lt;&gt;$E37),"y","")</f>
         <v/>
       </c>
     </row>
@@ -974,8 +978,8 @@
       <c r="E39" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F39" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E39,$B$2:$B$92,$B39,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E39,$B$2:$B$92,$B39,$D$2:$D$92,"Overtime")&gt;0,$E39&lt;&gt;$E38),"y","")</f>
+      <c r="F39" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B39,$E$2:$E92,$E39,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B39,$E$2:$E92,$E39,$D$2:$D92,"Overtime")&gt;0,$E39&lt;&gt;$E38),"y","")</f>
         <v/>
       </c>
     </row>
@@ -989,8 +993,8 @@
       <c r="E40" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F40" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E40,$B$2:$B$92,$B40,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E40,$B$2:$B$92,$B40,$D$2:$D$92,"Overtime")&gt;0,$E40&lt;&gt;$E39),"y","")</f>
+      <c r="F40" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B40,$E$2:$E92,$E40,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B40,$E$2:$E92,$E40,$D$2:$D92,"Overtime")&gt;0,$E40&lt;&gt;$E39),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1004,8 +1008,8 @@
       <c r="E41" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F41" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E41,$B$2:$B$92,$B41,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E41,$B$2:$B$92,$B41,$D$2:$D$92,"Overtime")&gt;0,$E41&lt;&gt;$E40),"y","")</f>
+      <c r="F41" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B41,$E$2:$E92,$E41,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B41,$E$2:$E92,$E41,$D$2:$D92,"Overtime")&gt;0,$E41&lt;&gt;$E40),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1019,8 +1023,8 @@
       <c r="E42" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F42" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E42,$B$2:$B$92,$B42,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E42,$B$2:$B$92,$B42,$D$2:$D$92,"Overtime")&gt;0,$E42&lt;&gt;$E41),"y","")</f>
+      <c r="F42" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B42,$E$2:$E92,$E42,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B42,$E$2:$E92,$E42,$D$2:$D92,"Overtime")&gt;0,$E42&lt;&gt;$E41),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1034,8 +1038,8 @@
       <c r="E43" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="F43" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E43,$B$2:$B$92,$B43,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E43,$B$2:$B$92,$B43,$D$2:$D$92,"Overtime")&gt;0,$E43&lt;&gt;$E42),"y","")</f>
+      <c r="F43" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B43,$E$2:$E92,$E43,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B43,$E$2:$E92,$E43,$D$2:$D92,"Overtime")&gt;0,$E43&lt;&gt;$E42),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1049,8 +1053,8 @@
       <c r="E44" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F44" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E44,$B$2:$B$92,$B44,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E44,$B$2:$B$92,$B44,$D$2:$D$92,"Overtime")&gt;0,$E44&lt;&gt;$E43),"y","")</f>
+      <c r="F44" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B44,$E$2:$E92,$E44,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B44,$E$2:$E92,$E44,$D$2:$D92,"Overtime")&gt;0,$E44&lt;&gt;$E43),"y","")</f>
         <v>y</v>
       </c>
     </row>
@@ -1064,8 +1068,8 @@
       <c r="E45" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F45" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E45,$B$2:$B$92,$B45,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E45,$B$2:$B$92,$B45,$D$2:$D$92,"Overtime")&gt;0,$E45&lt;&gt;$E44),"y","")</f>
+      <c r="F45" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B45,$E$2:$E92,$E45,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B45,$E$2:$E92,$E45,$D$2:$D92,"Overtime")&gt;0,$E45&lt;&gt;$E44),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1079,8 +1083,8 @@
       <c r="E46" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F46" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E46,$B$2:$B$92,$B46,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E46,$B$2:$B$92,$B46,$D$2:$D$92,"Overtime")&gt;0,$E46&lt;&gt;$E45),"y","")</f>
+      <c r="F46" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B46,$E$2:$E92,$E46,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B46,$E$2:$E92,$E46,$D$2:$D92,"Overtime")&gt;0,$E46&lt;&gt;$E45),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1094,8 +1098,8 @@
       <c r="E47" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F47" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E47,$B$2:$B$92,$B47,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E47,$B$2:$B$92,$B47,$D$2:$D$92,"Overtime")&gt;0,$E47&lt;&gt;$E46),"y","")</f>
+      <c r="F47" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B47,$E$2:$E92,$E47,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B47,$E$2:$E92,$E47,$D$2:$D92,"Overtime")&gt;0,$E47&lt;&gt;$E46),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1109,8 +1113,8 @@
       <c r="E48" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F48" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E48,$B$2:$B$92,$B48,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E48,$B$2:$B$92,$B48,$D$2:$D$92,"Overtime")&gt;0,$E48&lt;&gt;$E47),"y","")</f>
+      <c r="F48" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B48,$E$2:$E92,$E48,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B48,$E$2:$E92,$E48,$D$2:$D92,"Overtime")&gt;0,$E48&lt;&gt;$E47),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1124,8 +1128,8 @@
       <c r="E49" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F49" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E49,$B$2:$B$92,$B49,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E49,$B$2:$B$92,$B49,$D$2:$D$92,"Overtime")&gt;0,$E49&lt;&gt;$E48),"y","")</f>
+      <c r="F49" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B49,$E$2:$E92,$E49,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B49,$E$2:$E92,$E49,$D$2:$D92,"Overtime")&gt;0,$E49&lt;&gt;$E48),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1139,8 +1143,8 @@
       <c r="E50" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F50" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E50,$B$2:$B$92,$B50,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E50,$B$2:$B$92,$B50,$D$2:$D$92,"Overtime")&gt;0,$E50&lt;&gt;$E49),"y","")</f>
+      <c r="F50" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B50,$E$2:$E92,$E50,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B50,$E$2:$E92,$E50,$D$2:$D92,"Overtime")&gt;0,$E50&lt;&gt;$E49),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1154,8 +1158,8 @@
       <c r="E51" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F51" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E51,$B$2:$B$92,$B51,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E51,$B$2:$B$92,$B51,$D$2:$D$92,"Overtime")&gt;0,$E51&lt;&gt;$E50),"y","")</f>
+      <c r="F51" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B51,$E$2:$E92,$E51,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B51,$E$2:$E92,$E51,$D$2:$D92,"Overtime")&gt;0,$E51&lt;&gt;$E50),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1169,8 +1173,8 @@
       <c r="E52" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F52" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E52,$B$2:$B$92,$B52,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E52,$B$2:$B$92,$B52,$D$2:$D$92,"Overtime")&gt;0,$E52&lt;&gt;$E51),"y","")</f>
+      <c r="F52" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B52,$E$2:$E92,$E52,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B52,$E$2:$E92,$E52,$D$2:$D92,"Overtime")&gt;0,$E52&lt;&gt;$E51),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1184,8 +1188,8 @@
       <c r="E53" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F53" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E53,$B$2:$B$92,$B53,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E53,$B$2:$B$92,$B53,$D$2:$D$92,"Overtime")&gt;0,$E53&lt;&gt;$E52),"y","")</f>
+      <c r="F53" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B53,$E$2:$E92,$E53,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B53,$E$2:$E92,$E53,$D$2:$D92,"Overtime")&gt;0,$E53&lt;&gt;$E52),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1199,8 +1203,8 @@
       <c r="E54" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F54" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E54,$B$2:$B$92,$B54,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E54,$B$2:$B$92,$B54,$D$2:$D$92,"Overtime")&gt;0,$E54&lt;&gt;$E53),"y","")</f>
+      <c r="F54" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B54,$E$2:$E92,$E54,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B54,$E$2:$E92,$E54,$D$2:$D92,"Overtime")&gt;0,$E54&lt;&gt;$E53),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1214,8 +1218,8 @@
       <c r="E55" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F55" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E55,$B$2:$B$92,$B55,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E55,$B$2:$B$92,$B55,$D$2:$D$92,"Overtime")&gt;0,$E55&lt;&gt;$E54),"y","")</f>
+      <c r="F55" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B55,$E$2:$E92,$E55,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B55,$E$2:$E92,$E55,$D$2:$D92,"Overtime")&gt;0,$E55&lt;&gt;$E54),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1229,8 +1233,8 @@
       <c r="E56" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F56" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E56,$B$2:$B$92,$B56,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E56,$B$2:$B$92,$B56,$D$2:$D$92,"Overtime")&gt;0,$E56&lt;&gt;$E55),"y","")</f>
+      <c r="F56" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B56,$E$2:$E92,$E56,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B56,$E$2:$E92,$E56,$D$2:$D92,"Overtime")&gt;0,$E56&lt;&gt;$E55),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1244,8 +1248,8 @@
       <c r="E57" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F57" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E57,$B$2:$B$92,$B57,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E57,$B$2:$B$92,$B57,$D$2:$D$92,"Overtime")&gt;0,$E57&lt;&gt;$E56),"y","")</f>
+      <c r="F57" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B57,$E$2:$E92,$E57,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B57,$E$2:$E92,$E57,$D$2:$D92,"Overtime")&gt;0,$E57&lt;&gt;$E56),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1259,8 +1263,8 @@
       <c r="E58" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F58" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E58,$B$2:$B$92,$B58,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E58,$B$2:$B$92,$B58,$D$2:$D$92,"Overtime")&gt;0,$E58&lt;&gt;$E57),"y","")</f>
+      <c r="F58" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B58,$E$2:$E92,$E58,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B58,$E$2:$E92,$E58,$D$2:$D92,"Overtime")&gt;0,$E58&lt;&gt;$E57),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1274,8 +1278,8 @@
       <c r="E59" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F59" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E59,$B$2:$B$92,$B59,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E59,$B$2:$B$92,$B59,$D$2:$D$92,"Overtime")&gt;0,$E59&lt;&gt;$E58),"y","")</f>
+      <c r="F59" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B59,$E$2:$E92,$E59,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B59,$E$2:$E92,$E59,$D$2:$D92,"Overtime")&gt;0,$E59&lt;&gt;$E58),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1289,8 +1293,8 @@
       <c r="E60" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F60" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E60,$B$2:$B$92,$B60,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E60,$B$2:$B$92,$B60,$D$2:$D$92,"Overtime")&gt;0,$E60&lt;&gt;$E59),"y","")</f>
+      <c r="F60" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B60,$E$2:$E92,$E60,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B60,$E$2:$E92,$E60,$D$2:$D92,"Overtime")&gt;0,$E60&lt;&gt;$E59),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1304,8 +1308,8 @@
       <c r="E61" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F61" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E61,$B$2:$B$92,$B61,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E61,$B$2:$B$92,$B61,$D$2:$D$92,"Overtime")&gt;0,$E61&lt;&gt;$E60),"y","")</f>
+      <c r="F61" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B61,$E$2:$E92,$E61,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B61,$E$2:$E92,$E61,$D$2:$D92,"Overtime")&gt;0,$E61&lt;&gt;$E60),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1319,8 +1323,8 @@
       <c r="E62" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F62" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E62,$B$2:$B$92,$B62,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E62,$B$2:$B$92,$B62,$D$2:$D$92,"Overtime")&gt;0,$E62&lt;&gt;$E61),"y","")</f>
+      <c r="F62" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B62,$E$2:$E92,$E62,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B62,$E$2:$E92,$E62,$D$2:$D92,"Overtime")&gt;0,$E62&lt;&gt;$E61),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1334,8 +1338,8 @@
       <c r="E63" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F63" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E63,$B$2:$B$92,$B63,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E63,$B$2:$B$92,$B63,$D$2:$D$92,"Overtime")&gt;0,$E63&lt;&gt;$E62),"y","")</f>
+      <c r="F63" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B63,$E$2:$E92,$E63,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B63,$E$2:$E92,$E63,$D$2:$D92,"Overtime")&gt;0,$E63&lt;&gt;$E62),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1349,8 +1353,8 @@
       <c r="E64" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="F64" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E64,$B$2:$B$92,$B64,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E64,$B$2:$B$92,$B64,$D$2:$D$92,"Overtime")&gt;0,$E64&lt;&gt;$E63),"y","")</f>
+      <c r="F64" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B64,$E$2:$E92,$E64,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B64,$E$2:$E92,$E64,$D$2:$D92,"Overtime")&gt;0,$E64&lt;&gt;$E63),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1364,8 +1368,8 @@
       <c r="E65" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F65" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E65,$B$2:$B$92,$B65,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E65,$B$2:$B$92,$B65,$D$2:$D$92,"Overtime")&gt;0,$E65&lt;&gt;$E64),"y","")</f>
+      <c r="F65" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B65,$E$2:$E92,$E65,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B65,$E$2:$E92,$E65,$D$2:$D92,"Overtime")&gt;0,$E65&lt;&gt;$E64),"y","")</f>
         <v>y</v>
       </c>
     </row>
@@ -1379,8 +1383,8 @@
       <c r="E66" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F66" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E66,$B$2:$B$92,$B66,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E66,$B$2:$B$92,$B66,$D$2:$D$92,"Overtime")&gt;0,$E66&lt;&gt;$E65),"y","")</f>
+      <c r="F66" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B66,$E$2:$E92,$E66,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B66,$E$2:$E92,$E66,$D$2:$D92,"Overtime")&gt;0,$E66&lt;&gt;$E65),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1394,8 +1398,8 @@
       <c r="E67" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F67" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E67,$B$2:$B$92,$B67,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E67,$B$2:$B$92,$B67,$D$2:$D$92,"Overtime")&gt;0,$E67&lt;&gt;$E66),"y","")</f>
+      <c r="F67" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B67,$E$2:$E92,$E67,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B67,$E$2:$E92,$E67,$D$2:$D92,"Overtime")&gt;0,$E67&lt;&gt;$E66),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1409,8 +1413,8 @@
       <c r="E68" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F68" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E68,$B$2:$B$92,$B68,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E68,$B$2:$B$92,$B68,$D$2:$D$92,"Overtime")&gt;0,$E68&lt;&gt;$E67),"y","")</f>
+      <c r="F68" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B68,$E$2:$E92,$E68,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B68,$E$2:$E92,$E68,$D$2:$D92,"Overtime")&gt;0,$E68&lt;&gt;$E67),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1424,8 +1428,8 @@
       <c r="E69" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F69" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E69,$B$2:$B$92,$B69,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E69,$B$2:$B$92,$B69,$D$2:$D$92,"Overtime")&gt;0,$E69&lt;&gt;$E68),"y","")</f>
+      <c r="F69" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B69,$E$2:$E92,$E69,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B69,$E$2:$E92,$E69,$D$2:$D92,"Overtime")&gt;0,$E69&lt;&gt;$E68),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1439,8 +1443,8 @@
       <c r="E70" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="F70" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E70,$B$2:$B$92,$B70,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E70,$B$2:$B$92,$B70,$D$2:$D$92,"Overtime")&gt;0,$E70&lt;&gt;$E69),"y","")</f>
+      <c r="F70" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B70,$E$2:$E92,$E70,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B70,$E$2:$E92,$E70,$D$2:$D92,"Overtime")&gt;0,$E70&lt;&gt;$E69),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1454,8 +1458,8 @@
       <c r="E71" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F71" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E71,$B$2:$B$92,$B71,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E71,$B$2:$B$92,$B71,$D$2:$D$92,"Overtime")&gt;0,$E71&lt;&gt;$E70),"y","")</f>
+      <c r="F71" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B71,$E$2:$E92,$E71,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B71,$E$2:$E92,$E71,$D$2:$D92,"Overtime")&gt;0,$E71&lt;&gt;$E70),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1469,8 +1473,8 @@
       <c r="E72" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F72" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E72,$B$2:$B$92,$B72,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E72,$B$2:$B$92,$B72,$D$2:$D$92,"Overtime")&gt;0,$E72&lt;&gt;$E71),"y","")</f>
+      <c r="F72" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B72,$E$2:$E92,$E72,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B72,$E$2:$E92,$E72,$D$2:$D92,"Overtime")&gt;0,$E72&lt;&gt;$E71),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1484,8 +1488,8 @@
       <c r="E73" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="F73" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E73,$B$2:$B$92,$B73,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E73,$B$2:$B$92,$B73,$D$2:$D$92,"Overtime")&gt;0,$E73&lt;&gt;$E72),"y","")</f>
+      <c r="F73" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B73,$E$2:$E92,$E73,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B73,$E$2:$E92,$E73,$D$2:$D92,"Overtime")&gt;0,$E73&lt;&gt;$E72),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1499,8 +1503,8 @@
       <c r="E74" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="F74" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E74,$B$2:$B$92,$B74,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E74,$B$2:$B$92,$B74,$D$2:$D$92,"Overtime")&gt;0,$E74&lt;&gt;$E73),"y","")</f>
+      <c r="F74" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B74,$E$2:$E92,$E74,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B74,$E$2:$E92,$E74,$D$2:$D92,"Overtime")&gt;0,$E74&lt;&gt;$E73),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1514,8 +1518,8 @@
       <c r="E75" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F75" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E75,$B$2:$B$92,$B75,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E75,$B$2:$B$92,$B75,$D$2:$D$92,"Overtime")&gt;0,$E75&lt;&gt;$E74),"y","")</f>
+      <c r="F75" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B75,$E$2:$E92,$E75,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B75,$E$2:$E92,$E75,$D$2:$D92,"Overtime")&gt;0,$E75&lt;&gt;$E74),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1529,8 +1533,8 @@
       <c r="E76" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F76" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E76,$B$2:$B$92,$B76,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E76,$B$2:$B$92,$B76,$D$2:$D$92,"Overtime")&gt;0,$E76&lt;&gt;$E75),"y","")</f>
+      <c r="F76" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B76,$E$2:$E92,$E76,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B76,$E$2:$E92,$E76,$D$2:$D92,"Overtime")&gt;0,$E76&lt;&gt;$E75),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1544,8 +1548,8 @@
       <c r="E77" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F77" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E77,$B$2:$B$92,$B77,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E77,$B$2:$B$92,$B77,$D$2:$D$92,"Overtime")&gt;0,$E77&lt;&gt;$E76),"y","")</f>
+      <c r="F77" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B77,$E$2:$E92,$E77,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B77,$E$2:$E92,$E77,$D$2:$D92,"Overtime")&gt;0,$E77&lt;&gt;$E76),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1559,8 +1563,8 @@
       <c r="E78" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F78" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E78,$B$2:$B$92,$B78,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E78,$B$2:$B$92,$B78,$D$2:$D$92,"Overtime")&gt;0,$E78&lt;&gt;$E77),"y","")</f>
+      <c r="F78" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B78,$E$2:$E92,$E78,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B78,$E$2:$E92,$E78,$D$2:$D92,"Overtime")&gt;0,$E78&lt;&gt;$E77),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1574,8 +1578,8 @@
       <c r="E79" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F79" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E79,$B$2:$B$92,$B79,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E79,$B$2:$B$92,$B79,$D$2:$D$92,"Overtime")&gt;0,$E79&lt;&gt;$E78),"y","")</f>
+      <c r="F79" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B79,$E$2:$E92,$E79,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B79,$E$2:$E92,$E79,$D$2:$D92,"Overtime")&gt;0,$E79&lt;&gt;$E78),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1589,8 +1593,8 @@
       <c r="E80" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F80" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E80,$B$2:$B$92,$B80,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E80,$B$2:$B$92,$B80,$D$2:$D$92,"Overtime")&gt;0,$E80&lt;&gt;$E79),"y","")</f>
+      <c r="F80" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B80,$E$2:$E92,$E80,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B80,$E$2:$E92,$E80,$D$2:$D92,"Overtime")&gt;0,$E80&lt;&gt;$E79),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1604,8 +1608,8 @@
       <c r="E81" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="F81" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E81,$B$2:$B$92,$B81,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E81,$B$2:$B$92,$B81,$D$2:$D$92,"Overtime")&gt;0,$E81&lt;&gt;$E80),"y","")</f>
+      <c r="F81" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B81,$E$2:$E92,$E81,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B81,$E$2:$E92,$E81,$D$2:$D92,"Overtime")&gt;0,$E81&lt;&gt;$E80),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1619,8 +1623,8 @@
       <c r="E82" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F82" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E82,$B$2:$B$92,$B82,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E82,$B$2:$B$92,$B82,$D$2:$D$92,"Overtime")&gt;0,$E82&lt;&gt;$E81),"y","")</f>
+      <c r="F82" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B82,$E$2:$E92,$E82,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B82,$E$2:$E92,$E82,$D$2:$D92,"Overtime")&gt;0,$E82&lt;&gt;$E81),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1634,8 +1638,8 @@
       <c r="E83" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F83" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E83,$B$2:$B$92,$B83,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E83,$B$2:$B$92,$B83,$D$2:$D$92,"Overtime")&gt;0,$E83&lt;&gt;$E82),"y","")</f>
+      <c r="F83" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B83,$E$2:$E92,$E83,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B83,$E$2:$E92,$E83,$D$2:$D92,"Overtime")&gt;0,$E83&lt;&gt;$E82),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1649,8 +1653,8 @@
       <c r="E84" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F84" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E84,$B$2:$B$92,$B84,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E84,$B$2:$B$92,$B84,$D$2:$D$92,"Overtime")&gt;0,$E84&lt;&gt;$E83),"y","")</f>
+      <c r="F84" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B84,$E$2:$E92,$E84,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B84,$E$2:$E92,$E84,$D$2:$D92,"Overtime")&gt;0,$E84&lt;&gt;$E83),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1664,8 +1668,8 @@
       <c r="E85" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F85" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E85,$B$2:$B$92,$B85,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E85,$B$2:$B$92,$B85,$D$2:$D$92,"Overtime")&gt;0,$E85&lt;&gt;$E84),"y","")</f>
+      <c r="F85" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B85,$E$2:$E92,$E85,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B85,$E$2:$E92,$E85,$D$2:$D92,"Overtime")&gt;0,$E85&lt;&gt;$E84),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1679,8 +1683,8 @@
       <c r="E86" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F86" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E86,$B$2:$B$92,$B86,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E86,$B$2:$B$92,$B86,$D$2:$D$92,"Overtime")&gt;0,$E86&lt;&gt;$E85),"y","")</f>
+      <c r="F86" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B86,$E$2:$E92,$E86,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B86,$E$2:$E92,$E86,$D$2:$D92,"Overtime")&gt;0,$E86&lt;&gt;$E85),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1694,8 +1698,8 @@
       <c r="E87" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F87" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E87,$B$2:$B$92,$B87,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E87,$B$2:$B$92,$B87,$D$2:$D$92,"Overtime")&gt;0,$E87&lt;&gt;$E86),"y","")</f>
+      <c r="F87" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B87,$E$2:$E92,$E87,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B87,$E$2:$E92,$E87,$D$2:$D92,"Overtime")&gt;0,$E87&lt;&gt;$E86),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1709,8 +1713,8 @@
       <c r="E88" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="F88" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E88,$B$2:$B$92,$B88,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E88,$B$2:$B$92,$B88,$D$2:$D$92,"Overtime")&gt;0,$E88&lt;&gt;$E87),"y","")</f>
+      <c r="F88" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B88,$E$2:$E92,$E88,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B88,$E$2:$E92,$E88,$D$2:$D92,"Overtime")&gt;0,$E88&lt;&gt;$E87),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1724,8 +1728,8 @@
       <c r="E89" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F89" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E89,$B$2:$B$92,$B89,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E89,$B$2:$B$92,$B89,$D$2:$D$92,"Overtime")&gt;0,$E89&lt;&gt;$E88),"y","")</f>
+      <c r="F89" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B89,$E$2:$E92,$E89,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B89,$E$2:$E92,$E89,$D$2:$D92,"Overtime")&gt;0,$E89&lt;&gt;$E88),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1739,8 +1743,8 @@
       <c r="E90" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F90" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E90,$B$2:$B$92,$B90,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E90,$B$2:$B$92,$B90,$D$2:$D$92,"Overtime")&gt;0,$E90&lt;&gt;$E89),"y","")</f>
+      <c r="F90" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B90,$E$2:$E92,$E90,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B90,$E$2:$E92,$E90,$D$2:$D92,"Overtime")&gt;0,$E90&lt;&gt;$E89),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1754,8 +1758,8 @@
       <c r="E91" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F91" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E91,$B$2:$B$92,$B91,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E91,$B$2:$B$92,$B91,$D$2:$D$92,"Overtime")&gt;0,$E91&lt;&gt;$E90),"y","")</f>
+      <c r="F91" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B91,$E$2:$E92,$E91,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B91,$E$2:$E92,$E91,$D$2:$D92,"Overtime")&gt;0,$E91&lt;&gt;$E90),"y","")</f>
         <v/>
       </c>
     </row>
@@ -1769,8 +1773,8 @@
       <c r="E92" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="F92" s="0" t="str">
-        <f aca="false">IF(AND(COUNTIFS($E$2:$E$92,$E92,$B$2:$B$92,$B92,$C$2:$C$92,"Sick Day")&gt;0,COUNTIFS($E$2:$E$92,$E92,$B$2:$B$92,$B92,$D$2:$D$92,"Overtime")&gt;0,$E92&lt;&gt;$E91),"y","")</f>
+      <c r="F92" s="4" t="str">
+        <f aca="false">IF(AND(COUNTIFS($B$2:$B92,$B92,$E$2:$E92,$E92,$C$2:$C92,"Sick Day")&gt;0,COUNTIFS($B$2:$B92,$B92,$E$2:$E92,$E92,$D$2:$D92,"Overtime")&gt;0,$E92&lt;&gt;$E91),"y","")</f>
         <v/>
       </c>
     </row>
